--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
